--- a/tests/testset/testset_app.xlsx
+++ b/tests/testset/testset_app.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsrlnl-my.sharepoint.com/personal/s_kapinga_wsrl_nl/Documents/Documenten/Github/GeoProb-Pipe/tests/testset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="11_ADE90F4B27C7C86E885C62DA4C9A1E92DA8D07F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3886C4CE-6454-4AA3-967D-FD6C215CC6E4}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="11_ADE90F4B27C7C86E885C62DA4C9A1E92DA8D07F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0FC6E95-17AD-4C40-AAD8-843131802643}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3135" windowWidth="24585" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29040" yWindow="3915" windowWidth="24585" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="theta">'Constanten'!$E$6</definedName>
     <definedName name="v">'Constanten'!$E$9</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1230,31 +1230,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
+      <border outline="0">
+        <top style="thin">
           <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1262,13 +1241,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -1301,16 +1273,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1343,16 +1315,44 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color auto="1"/>
-        </top>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1369,7 +1369,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{041F15A6-CF32-4D3B-B676-34E6571E0971}" name="Vakken" displayName="Vakken" ref="A1:J90" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{041F15A6-CF32-4D3B-B676-34E6571E0971}" name="Vakken" displayName="Vakken" ref="A1:J90" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:J90" xr:uid="{041F15A6-CF32-4D3B-B676-34E6571E0971}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{74D2F176-4646-4AE0-B6F4-08D4E6C28D16}" name="VakID"/>
@@ -1388,7 +1388,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9207402-924B-4CC0-BFE8-2742B189FE45}" name="Uittredepunten" displayName="Uittredepunten" ref="A1:T1180" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9207402-924B-4CC0-BFE8-2742B189FE45}" name="Uittredepunten" displayName="Uittredepunten" ref="A1:T1180" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A1:T1180" xr:uid="{E9207402-924B-4CC0-BFE8-2742B189FE45}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{9BC33A70-EA76-4303-87DF-06358F941718}" name="UittredepuntID"/>
@@ -1417,7 +1417,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3993CD63-E076-4278-844B-A7A048F56AE6}" name="Ondergrondscenarios" displayName="Ondergrondscenarios" ref="A1:P535" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3993CD63-E076-4278-844B-A7A048F56AE6}" name="Ondergrondscenarios" displayName="Ondergrondscenarios" ref="A1:P535" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:P535" xr:uid="{3993CD63-E076-4278-844B-A7A048F56AE6}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{0E1CDA33-5849-4195-ADD5-BF53936D0AD2}" name="OndergrondscenarioID"/>
@@ -4651,25 +4651,25 @@
   <dimension ref="A1:T1180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" customWidth="1"/>
-    <col min="15" max="15" width="22.140625" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
-    <col min="17" max="17" width="22.140625" customWidth="1"/>
-    <col min="18" max="18" width="22" customWidth="1"/>
-    <col min="19" max="19" width="22.140625" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
